--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753718880_h_4.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02382399986743669</v>
+        <v>0.01402734682566982</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008423128287666226</v>
+        <v>0.00840949336849749</v>
       </c>
       <c r="C2" t="n">
-        <v>25251912</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25251912</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>17689679</v>
+        <v>4514315</v>
       </c>
       <c r="L2" t="n">
-        <v>9749766</v>
+        <v>2519504</v>
       </c>
       <c r="M2" t="n">
-        <v>2246262</v>
+        <v>583337</v>
       </c>
       <c r="N2" t="n">
-        <v>75188</v>
+        <v>18285</v>
       </c>
       <c r="O2" t="n">
-        <v>1343701</v>
+        <v>345680</v>
       </c>
       <c r="P2" t="n">
-        <v>527262</v>
+        <v>132853</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999939799308777</v>
+        <v>0.9999963641166687</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8665348887443542</v>
+        <v>0.876150906085968</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7315648794174194</v>
+        <v>0.754357635974884</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6590500473976135</v>
+        <v>0.6827589869499207</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1895733177661896</v>
+        <v>0.1895015090703964</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7150898575782776</v>
+        <v>0.7357820868492126</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8228530287742615</v>
+        <v>0.8486894369125366</v>
       </c>
       <c r="X2" t="n">
-        <v>25251912</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25251912</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>19271788</v>
+        <v>4843813</v>
       </c>
       <c r="AG2" t="n">
-        <v>11873762</v>
+        <v>2988574</v>
       </c>
       <c r="AH2" t="n">
-        <v>3197356</v>
+        <v>801351</v>
       </c>
       <c r="AI2" t="n">
-        <v>235916</v>
+        <v>59120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1836054</v>
+        <v>459465</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566228985786438</v>
+        <v>0.9564417004585266</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112591743469238</v>
+        <v>0.9113976359367371</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.858102023601532</v>
+        <v>0.8579177856445312</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624639630317688</v>
+        <v>0.6617860794067383</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020282030105591</v>
+        <v>0.9019746780395508</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.005719117379125712</v>
+        <v>0.003186926269829494</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002019936826367219</v>
+        <v>0.002015272774735009</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>17689679</v>
+        <v>4514315</v>
       </c>
       <c r="E3" t="n">
-        <v>2392691</v>
+        <v>537447</v>
       </c>
       <c r="F3" t="n">
-        <v>36946</v>
+        <v>5646</v>
       </c>
       <c r="G3" t="n">
-        <v>3427</v>
+        <v>604</v>
       </c>
       <c r="H3" t="n">
-        <v>2119</v>
+        <v>237</v>
       </c>
       <c r="I3" t="n">
-        <v>97</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>40066336</v>
+        <v>10069597</v>
       </c>
       <c r="K3" t="n">
-        <v>42468840</v>
+        <v>10719615</v>
       </c>
       <c r="L3" t="n">
-        <v>48693142</v>
+        <v>12311035</v>
       </c>
       <c r="M3" t="n">
-        <v>60428452</v>
+        <v>15210435</v>
       </c>
       <c r="N3" t="n">
-        <v>64640582</v>
+        <v>16248422</v>
       </c>
       <c r="O3" t="n">
-        <v>62746721</v>
+        <v>15782282</v>
       </c>
       <c r="P3" t="n">
-        <v>64431697</v>
+        <v>16198968</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8789917230606079</v>
+        <v>0.8924639821052551</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7472373843193054</v>
+        <v>0.7670806646347046</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6025579571723938</v>
+        <v>0.6242102980613708</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2109717130661011</v>
+        <v>0.2045919895172119</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6598692536354065</v>
+        <v>0.6783559322357178</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6819289326667786</v>
+        <v>0.6871256828308105</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19271788</v>
+        <v>4843813</v>
       </c>
       <c r="Z3" t="n">
-        <v>791602</v>
+        <v>198937</v>
       </c>
       <c r="AA3" t="n">
-        <v>34131</v>
+        <v>8593</v>
       </c>
       <c r="AB3" t="n">
-        <v>27146</v>
+        <v>6842</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>40066488</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>44319573</v>
+        <v>11137143</v>
       </c>
       <c r="AG3" t="n">
-        <v>51114353</v>
+        <v>12840927</v>
       </c>
       <c r="AH3" t="n">
-        <v>61061800</v>
+        <v>15348766</v>
       </c>
       <c r="AI3" t="n">
-        <v>64841808</v>
+        <v>16296413</v>
       </c>
       <c r="AJ3" t="n">
-        <v>63082667</v>
+        <v>15856481</v>
       </c>
       <c r="AK3" t="n">
-        <v>64492192</v>
+        <v>16209400</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576059579849243</v>
+        <v>0.9576045870780945</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100238084793091</v>
+        <v>0.9098923206329346</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576881885528564</v>
+        <v>0.8575001358985901</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.66196209192276</v>
+        <v>0.6614972949028015</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016556143760681</v>
+        <v>0.9016454815864563</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.06025320929543993</v>
+        <v>0.04397611357444111</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0318805782860274</v>
+        <v>0.031840082348875</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>2570782</v>
+        <v>602703</v>
       </c>
       <c r="E4" t="n">
-        <v>9749766</v>
+        <v>2519504</v>
       </c>
       <c r="F4" t="n">
-        <v>650774</v>
+        <v>148575</v>
       </c>
       <c r="G4" t="n">
-        <v>26699</v>
+        <v>5170</v>
       </c>
       <c r="H4" t="n">
-        <v>45866</v>
+        <v>8042</v>
       </c>
       <c r="I4" t="n">
-        <v>3861</v>
+        <v>542</v>
       </c>
       <c r="J4" t="n">
-        <v>152</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
-        <v>2724593</v>
+        <v>638125</v>
       </c>
       <c r="L4" t="n">
-        <v>3577509</v>
+        <v>820429</v>
       </c>
       <c r="M4" t="n">
-        <v>1162071</v>
+        <v>271045</v>
       </c>
       <c r="N4" t="n">
-        <v>321429</v>
+        <v>78205</v>
       </c>
       <c r="O4" t="n">
-        <v>535365</v>
+        <v>124133</v>
       </c>
       <c r="P4" t="n">
-        <v>113511</v>
+        <v>23686</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999969601631165</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.872718870639801</v>
+        <v>0.884232223033905</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7393180727958679</v>
+        <v>0.7606658935546875</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6295391917228699</v>
+        <v>0.6521732211112976</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1997009366750717</v>
+        <v>0.1967578083276749</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6863706707954407</v>
+        <v>0.7059029936790466</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7457921504974365</v>
+        <v>0.759409487247467</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>815845</v>
+        <v>205971</v>
       </c>
       <c r="Z4" t="n">
-        <v>11873762</v>
+        <v>2988574</v>
       </c>
       <c r="AA4" t="n">
-        <v>331353</v>
+        <v>83251</v>
       </c>
       <c r="AB4" t="n">
-        <v>21937</v>
+        <v>5524</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>873860</v>
+        <v>220597</v>
       </c>
       <c r="AG4" t="n">
-        <v>1156298</v>
+        <v>290537</v>
       </c>
       <c r="AH4" t="n">
-        <v>528723</v>
+        <v>132714</v>
       </c>
       <c r="AI4" t="n">
-        <v>120203</v>
+        <v>30214</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199419</v>
+        <v>49934</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571141600608826</v>
+        <v>0.9570227861404419</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910641074180603</v>
+        <v>0.9106442928314209</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578950166702271</v>
+        <v>0.8577089309692383</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622129082679749</v>
+        <v>0.6616416573524475</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018418788909912</v>
+        <v>0.9018100500106812</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>100806</v>
+        <v>22394</v>
       </c>
       <c r="E5" t="n">
-        <v>1026098</v>
+        <v>249870</v>
       </c>
       <c r="F5" t="n">
-        <v>2246262</v>
+        <v>583337</v>
       </c>
       <c r="G5" t="n">
-        <v>103876</v>
+        <v>23507</v>
       </c>
       <c r="H5" t="n">
-        <v>231475</v>
+        <v>51852</v>
       </c>
       <c r="I5" t="n">
-        <v>19356</v>
+        <v>3558</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2435288</v>
+        <v>543945</v>
       </c>
       <c r="L5" t="n">
-        <v>3297983</v>
+        <v>765032</v>
       </c>
       <c r="M5" t="n">
-        <v>1481615</v>
+        <v>351183</v>
       </c>
       <c r="N5" t="n">
-        <v>281201</v>
+        <v>71088</v>
       </c>
       <c r="O5" t="n">
-        <v>692613</v>
+        <v>163905</v>
       </c>
       <c r="P5" t="n">
-        <v>245930</v>
+        <v>60493</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999976754188538</v>
+        <v>0.9999985694885254</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9210041761398315</v>
+        <v>0.9279928207397461</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8947387933731079</v>
+        <v>0.9034197926521301</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9595261812210083</v>
+        <v>0.9620962738990784</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9907739758491516</v>
+        <v>0.9909056425094604</v>
       </c>
       <c r="V5" t="n">
-        <v>0.981200098991394</v>
+        <v>0.9824538230895996</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9944971203804016</v>
+        <v>0.9948721528053284</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>32012</v>
+        <v>8071</v>
       </c>
       <c r="Z5" t="n">
-        <v>339750</v>
+        <v>85325</v>
       </c>
       <c r="AA5" t="n">
-        <v>3197356</v>
+        <v>801351</v>
       </c>
       <c r="AB5" t="n">
-        <v>39755</v>
+        <v>9981</v>
       </c>
       <c r="AC5" t="n">
-        <v>116472</v>
+        <v>29159</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>853179</v>
+        <v>214447</v>
       </c>
       <c r="AG5" t="n">
-        <v>1173987</v>
+        <v>295962</v>
       </c>
       <c r="AH5" t="n">
-        <v>530521</v>
+        <v>133169</v>
       </c>
       <c r="AI5" t="n">
-        <v>120473</v>
+        <v>30253</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200260</v>
+        <v>50120</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735596776008606</v>
+        <v>0.9734987616539001</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643242359161377</v>
+        <v>0.9642727375030518</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837833642959595</v>
+        <v>0.9838034510612488</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963153600692749</v>
+        <v>0.9963165521621704</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938810467720032</v>
+        <v>0.9939050674438477</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998375415802002</v>
+        <v>0.9983825087547302</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>51344</v>
+        <v>12978</v>
       </c>
       <c r="E6" t="n">
-        <v>78511</v>
+        <v>18899</v>
       </c>
       <c r="F6" t="n">
-        <v>110663</v>
+        <v>29921</v>
       </c>
       <c r="G6" t="n">
-        <v>75188</v>
+        <v>18285</v>
       </c>
       <c r="H6" t="n">
-        <v>37388</v>
+        <v>8665</v>
       </c>
       <c r="I6" t="n">
-        <v>3274</v>
+        <v>619</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25780</v>
+        <v>6499</v>
       </c>
       <c r="Z6" t="n">
-        <v>21382</v>
+        <v>5384</v>
       </c>
       <c r="AA6" t="n">
-        <v>43482</v>
+        <v>10901</v>
       </c>
       <c r="AB6" t="n">
-        <v>235916</v>
+        <v>59120</v>
       </c>
       <c r="AC6" t="n">
-        <v>27905</v>
+        <v>6988</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1558</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>76021</v>
+        <v>13622</v>
       </c>
       <c r="F7" t="n">
-        <v>348756</v>
+        <v>84125</v>
       </c>
       <c r="G7" t="n">
-        <v>179303</v>
+        <v>47177</v>
       </c>
       <c r="H7" t="n">
-        <v>1343701</v>
+        <v>345680</v>
       </c>
       <c r="I7" t="n">
-        <v>86923</v>
+        <v>18958</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3240</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118437</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30304</v>
+        <v>7601</v>
       </c>
       <c r="AC7" t="n">
-        <v>1836054</v>
+        <v>459465</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="E8" t="n">
-        <v>4188</v>
+        <v>591</v>
       </c>
       <c r="F8" t="n">
-        <v>14932</v>
+        <v>2778</v>
       </c>
       <c r="G8" t="n">
-        <v>8124</v>
+        <v>1747</v>
       </c>
       <c r="H8" t="n">
-        <v>218517</v>
+        <v>55337</v>
       </c>
       <c r="I8" t="n">
-        <v>527262</v>
+        <v>132853</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
